--- a/data/san_antonio_bajo.xlsx
+++ b/data/san_antonio_bajo.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J15"/>
+  <dimension ref="A1:M15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -457,25 +457,40 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>05dec2025</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>06dec2025</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>07dec2025</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
           <t>26nov2025</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>27nov2025</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>28nov2025</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>29nov2025</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>30nov2025</t>
         </is>
@@ -500,18 +515,27 @@
         <v>10</v>
       </c>
       <c r="F2" t="n">
+        <v>16</v>
+      </c>
+      <c r="G2" t="n">
+        <v>3</v>
+      </c>
+      <c r="H2" t="n">
+        <v>3</v>
+      </c>
+      <c r="I2" t="n">
         <v>5</v>
       </c>
-      <c r="G2" t="n">
+      <c r="J2" t="n">
         <v>4</v>
       </c>
-      <c r="H2" t="n">
-        <v>11</v>
-      </c>
-      <c r="I2" t="n">
-        <v>11</v>
-      </c>
-      <c r="J2" t="n">
+      <c r="K2" t="n">
+        <v>11</v>
+      </c>
+      <c r="L2" t="n">
+        <v>11</v>
+      </c>
+      <c r="M2" t="n">
         <v>11</v>
       </c>
     </row>
@@ -534,18 +558,27 @@
         <v>12</v>
       </c>
       <c r="F3" t="n">
+        <v>12</v>
+      </c>
+      <c r="G3" t="n">
+        <v>14</v>
+      </c>
+      <c r="H3" t="n">
+        <v>7</v>
+      </c>
+      <c r="I3" t="n">
         <v>5</v>
       </c>
-      <c r="G3" t="n">
-        <v>10</v>
-      </c>
-      <c r="H3" t="n">
-        <v>10</v>
-      </c>
-      <c r="I3" t="n">
-        <v>10</v>
-      </c>
       <c r="J3" t="n">
+        <v>10</v>
+      </c>
+      <c r="K3" t="n">
+        <v>10</v>
+      </c>
+      <c r="L3" t="n">
+        <v>10</v>
+      </c>
+      <c r="M3" t="n">
         <v>2</v>
       </c>
     </row>
@@ -568,18 +601,27 @@
         <v>12</v>
       </c>
       <c r="F4" t="n">
+        <v>17</v>
+      </c>
+      <c r="G4" t="n">
+        <v>10</v>
+      </c>
+      <c r="H4" t="n">
+        <v>10</v>
+      </c>
+      <c r="I4" t="n">
         <v>5</v>
       </c>
-      <c r="G4" t="n">
-        <v>11</v>
-      </c>
-      <c r="H4" t="n">
-        <v>11</v>
-      </c>
-      <c r="I4" t="n">
+      <c r="J4" t="n">
+        <v>11</v>
+      </c>
+      <c r="K4" t="n">
+        <v>11</v>
+      </c>
+      <c r="L4" t="n">
         <v>2</v>
       </c>
-      <c r="J4" t="n">
+      <c r="M4" t="n">
         <v>11</v>
       </c>
     </row>
@@ -602,18 +644,27 @@
         <v>11</v>
       </c>
       <c r="F5" t="n">
+        <v>10</v>
+      </c>
+      <c r="G5" t="n">
+        <v>10</v>
+      </c>
+      <c r="H5" t="n">
+        <v>13</v>
+      </c>
+      <c r="I5" t="n">
         <v>5</v>
       </c>
-      <c r="G5" t="n">
-        <v>11</v>
-      </c>
-      <c r="H5" t="n">
-        <v>11</v>
-      </c>
-      <c r="I5" t="n">
-        <v>11</v>
-      </c>
       <c r="J5" t="n">
+        <v>11</v>
+      </c>
+      <c r="K5" t="n">
+        <v>11</v>
+      </c>
+      <c r="L5" t="n">
+        <v>11</v>
+      </c>
+      <c r="M5" t="n">
         <v>10</v>
       </c>
     </row>
@@ -636,18 +687,27 @@
         <v>11</v>
       </c>
       <c r="F6" t="n">
+        <v>12</v>
+      </c>
+      <c r="G6" t="n">
+        <v>13</v>
+      </c>
+      <c r="H6" t="n">
+        <v>10</v>
+      </c>
+      <c r="I6" t="n">
         <v>5</v>
       </c>
-      <c r="G6" t="n">
-        <v>11</v>
-      </c>
-      <c r="H6" t="n">
-        <v>11</v>
-      </c>
-      <c r="I6" t="n">
-        <v>10</v>
-      </c>
       <c r="J6" t="n">
+        <v>11</v>
+      </c>
+      <c r="K6" t="n">
+        <v>11</v>
+      </c>
+      <c r="L6" t="n">
+        <v>10</v>
+      </c>
+      <c r="M6" t="n">
         <v>12</v>
       </c>
     </row>
@@ -670,18 +730,27 @@
         <v>13</v>
       </c>
       <c r="F7" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="n">
+        <v>4</v>
+      </c>
+      <c r="I7" t="n">
+        <v>5</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
         <v>21</v>
       </c>
-      <c r="I7" t="n">
+      <c r="L7" t="n">
         <v>12</v>
       </c>
-      <c r="J7" t="n">
+      <c r="M7" t="n">
         <v>11</v>
       </c>
     </row>
@@ -713,9 +782,18 @@
         <v>0</v>
       </c>
       <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
         <v>24</v>
       </c>
-      <c r="J8" t="n">
+      <c r="M8" t="n">
         <v>20</v>
       </c>
     </row>
@@ -738,18 +816,27 @@
         <v>10</v>
       </c>
       <c r="F9" t="n">
+        <v>9</v>
+      </c>
+      <c r="G9" t="n">
+        <v>11</v>
+      </c>
+      <c r="H9" t="n">
+        <v>11</v>
+      </c>
+      <c r="I9" t="n">
         <v>5</v>
       </c>
-      <c r="G9" t="n">
-        <v>10</v>
-      </c>
-      <c r="H9" t="n">
-        <v>11</v>
-      </c>
-      <c r="I9" t="n">
-        <v>10</v>
-      </c>
       <c r="J9" t="n">
+        <v>10</v>
+      </c>
+      <c r="K9" t="n">
+        <v>11</v>
+      </c>
+      <c r="L9" t="n">
+        <v>10</v>
+      </c>
+      <c r="M9" t="n">
         <v>10</v>
       </c>
     </row>
@@ -772,18 +859,27 @@
         <v>11</v>
       </c>
       <c r="F10" t="n">
+        <v>10</v>
+      </c>
+      <c r="G10" t="n">
+        <v>10</v>
+      </c>
+      <c r="H10" t="n">
+        <v>13</v>
+      </c>
+      <c r="I10" t="n">
         <v>6</v>
       </c>
-      <c r="G10" t="n">
+      <c r="J10" t="n">
         <v>9</v>
       </c>
-      <c r="H10" t="n">
-        <v>11</v>
-      </c>
-      <c r="I10" t="n">
-        <v>11</v>
-      </c>
-      <c r="J10" t="n">
+      <c r="K10" t="n">
+        <v>11</v>
+      </c>
+      <c r="L10" t="n">
+        <v>11</v>
+      </c>
+      <c r="M10" t="n">
         <v>10</v>
       </c>
     </row>
@@ -806,18 +902,27 @@
         <v>10</v>
       </c>
       <c r="F11" t="n">
+        <v>15</v>
+      </c>
+      <c r="G11" t="n">
+        <v>3</v>
+      </c>
+      <c r="H11" t="n">
+        <v>4</v>
+      </c>
+      <c r="I11" t="n">
         <v>5</v>
       </c>
-      <c r="G11" t="n">
-        <v>11</v>
-      </c>
-      <c r="H11" t="n">
-        <v>11</v>
-      </c>
-      <c r="I11" t="n">
-        <v>11</v>
-      </c>
       <c r="J11" t="n">
+        <v>11</v>
+      </c>
+      <c r="K11" t="n">
+        <v>11</v>
+      </c>
+      <c r="L11" t="n">
+        <v>11</v>
+      </c>
+      <c r="M11" t="n">
         <v>11</v>
       </c>
     </row>
@@ -840,18 +945,27 @@
         <v>15</v>
       </c>
       <c r="F12" t="n">
+        <v>7</v>
+      </c>
+      <c r="G12" t="n">
+        <v>3</v>
+      </c>
+      <c r="H12" t="n">
         <v>5</v>
       </c>
-      <c r="G12" t="n">
-        <v>11</v>
-      </c>
-      <c r="H12" t="n">
-        <v>11</v>
-      </c>
       <c r="I12" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J12" t="n">
+        <v>11</v>
+      </c>
+      <c r="K12" t="n">
+        <v>11</v>
+      </c>
+      <c r="L12" t="n">
+        <v>10</v>
+      </c>
+      <c r="M12" t="n">
         <v>11</v>
       </c>
     </row>
@@ -874,18 +988,27 @@
         <v>10</v>
       </c>
       <c r="F13" t="n">
+        <v>12</v>
+      </c>
+      <c r="G13" t="n">
+        <v>10</v>
+      </c>
+      <c r="H13" t="n">
+        <v>11</v>
+      </c>
+      <c r="I13" t="n">
         <v>5</v>
       </c>
-      <c r="G13" t="n">
-        <v>11</v>
-      </c>
-      <c r="H13" t="n">
-        <v>11</v>
-      </c>
-      <c r="I13" t="n">
-        <v>11</v>
-      </c>
       <c r="J13" t="n">
+        <v>11</v>
+      </c>
+      <c r="K13" t="n">
+        <v>11</v>
+      </c>
+      <c r="L13" t="n">
+        <v>11</v>
+      </c>
+      <c r="M13" t="n">
         <v>11</v>
       </c>
     </row>
@@ -908,18 +1031,27 @@
         <v>10</v>
       </c>
       <c r="F14" t="n">
+        <v>10</v>
+      </c>
+      <c r="G14" t="n">
+        <v>10</v>
+      </c>
+      <c r="H14" t="n">
+        <v>10</v>
+      </c>
+      <c r="I14" t="n">
         <v>0</v>
       </c>
-      <c r="G14" t="n">
-        <v>10</v>
-      </c>
-      <c r="H14" t="n">
-        <v>11</v>
-      </c>
-      <c r="I14" t="n">
-        <v>11</v>
-      </c>
       <c r="J14" t="n">
+        <v>10</v>
+      </c>
+      <c r="K14" t="n">
+        <v>11</v>
+      </c>
+      <c r="L14" t="n">
+        <v>11</v>
+      </c>
+      <c r="M14" t="n">
         <v>10</v>
       </c>
     </row>
@@ -942,18 +1074,27 @@
         <v>14</v>
       </c>
       <c r="F15" t="n">
+        <v>15</v>
+      </c>
+      <c r="G15" t="n">
+        <v>15</v>
+      </c>
+      <c r="H15" t="n">
+        <v>12</v>
+      </c>
+      <c r="I15" t="n">
         <v>5</v>
       </c>
-      <c r="G15" t="n">
-        <v>11</v>
-      </c>
-      <c r="H15" t="n">
-        <v>11</v>
-      </c>
-      <c r="I15" t="n">
-        <v>11</v>
-      </c>
       <c r="J15" t="n">
+        <v>11</v>
+      </c>
+      <c r="K15" t="n">
+        <v>11</v>
+      </c>
+      <c r="L15" t="n">
+        <v>11</v>
+      </c>
+      <c r="M15" t="n">
         <v>12</v>
       </c>
     </row>
@@ -968,7 +1109,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J15"/>
+  <dimension ref="A1:M15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -999,25 +1140,40 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>05dec2025</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>06dec2025</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>07dec2025</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
           <t>26nov2025</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>27nov2025</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>28nov2025</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>29nov2025</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>30nov2025</t>
         </is>
@@ -1047,25 +1203,40 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
         <is>
           <t>11</t>
         </is>
@@ -1099,25 +1270,40 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
       <c r="J3" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
         <is>
           <t>2</t>
         </is>
@@ -1151,25 +1337,40 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>11</t>
         </is>
@@ -1203,25 +1404,40 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
       <c r="J5" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
         <is>
           <t>10</t>
         </is>
@@ -1255,25 +1471,40 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
       <c r="J6" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
         <is>
           <t>12</t>
         </is>
@@ -1307,21 +1538,32 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
           <t>21</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>11</t>
         </is>
@@ -1344,12 +1586,15 @@
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr">
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>20</t>
         </is>
@@ -1383,25 +1628,40 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
       <c r="J9" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
         <is>
           <t>10</t>
         </is>
@@ -1435,25 +1695,40 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="J10" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
         <is>
           <t>10</t>
         </is>
@@ -1487,25 +1762,40 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
       <c r="J11" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
         <is>
           <t>11</t>
         </is>
@@ -1539,25 +1829,40 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
         <is>
           <t>11</t>
         </is>
@@ -1591,25 +1896,40 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
       <c r="J13" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
         <is>
           <t>11</t>
         </is>
@@ -1641,7 +1961,11 @@
           <t>10</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr"/>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="G14" t="inlineStr">
         <is>
           <t>10</t>
@@ -1649,15 +1973,26 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
         <is>
           <t>10</t>
         </is>
@@ -1691,25 +2026,40 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
       <c r="J15" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
         <is>
           <t>12</t>
         </is>

--- a/data/san_antonio_bajo.xlsx
+++ b/data/san_antonio_bajo.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M15"/>
+  <dimension ref="A1:O15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -472,25 +472,35 @@
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
+          <t>08dec2025</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>09dec2025</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
           <t>26nov2025</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>27nov2025</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>28nov2025</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>29nov2025</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>30nov2025</t>
         </is>
@@ -524,18 +534,24 @@
         <v>3</v>
       </c>
       <c r="I2" t="n">
+        <v>12</v>
+      </c>
+      <c r="J2" t="n">
         <v>5</v>
       </c>
-      <c r="J2" t="n">
+      <c r="K2" t="n">
+        <v>5</v>
+      </c>
+      <c r="L2" t="n">
         <v>4</v>
       </c>
-      <c r="K2" t="n">
-        <v>11</v>
-      </c>
-      <c r="L2" t="n">
-        <v>11</v>
-      </c>
       <c r="M2" t="n">
+        <v>11</v>
+      </c>
+      <c r="N2" t="n">
+        <v>11</v>
+      </c>
+      <c r="O2" t="n">
         <v>11</v>
       </c>
     </row>
@@ -567,18 +583,24 @@
         <v>7</v>
       </c>
       <c r="I3" t="n">
+        <v>7</v>
+      </c>
+      <c r="J3" t="n">
+        <v>8</v>
+      </c>
+      <c r="K3" t="n">
         <v>5</v>
       </c>
-      <c r="J3" t="n">
-        <v>10</v>
-      </c>
-      <c r="K3" t="n">
-        <v>10</v>
-      </c>
       <c r="L3" t="n">
         <v>10</v>
       </c>
       <c r="M3" t="n">
+        <v>10</v>
+      </c>
+      <c r="N3" t="n">
+        <v>10</v>
+      </c>
+      <c r="O3" t="n">
         <v>2</v>
       </c>
     </row>
@@ -610,18 +632,24 @@
         <v>10</v>
       </c>
       <c r="I4" t="n">
+        <v>10</v>
+      </c>
+      <c r="J4" t="n">
+        <v>9</v>
+      </c>
+      <c r="K4" t="n">
         <v>5</v>
       </c>
-      <c r="J4" t="n">
-        <v>11</v>
-      </c>
-      <c r="K4" t="n">
-        <v>11</v>
-      </c>
       <c r="L4" t="n">
+        <v>11</v>
+      </c>
+      <c r="M4" t="n">
+        <v>11</v>
+      </c>
+      <c r="N4" t="n">
         <v>2</v>
       </c>
-      <c r="M4" t="n">
+      <c r="O4" t="n">
         <v>11</v>
       </c>
     </row>
@@ -653,18 +681,24 @@
         <v>13</v>
       </c>
       <c r="I5" t="n">
+        <v>10</v>
+      </c>
+      <c r="J5" t="n">
+        <v>10</v>
+      </c>
+      <c r="K5" t="n">
         <v>5</v>
       </c>
-      <c r="J5" t="n">
-        <v>11</v>
-      </c>
-      <c r="K5" t="n">
-        <v>11</v>
-      </c>
       <c r="L5" t="n">
         <v>11</v>
       </c>
       <c r="M5" t="n">
+        <v>11</v>
+      </c>
+      <c r="N5" t="n">
+        <v>11</v>
+      </c>
+      <c r="O5" t="n">
         <v>10</v>
       </c>
     </row>
@@ -696,18 +730,24 @@
         <v>10</v>
       </c>
       <c r="I6" t="n">
+        <v>9</v>
+      </c>
+      <c r="J6" t="n">
+        <v>8</v>
+      </c>
+      <c r="K6" t="n">
         <v>5</v>
       </c>
-      <c r="J6" t="n">
-        <v>11</v>
-      </c>
-      <c r="K6" t="n">
-        <v>11</v>
-      </c>
       <c r="L6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M6" t="n">
+        <v>11</v>
+      </c>
+      <c r="N6" t="n">
+        <v>10</v>
+      </c>
+      <c r="O6" t="n">
         <v>12</v>
       </c>
     </row>
@@ -739,18 +779,24 @@
         <v>4</v>
       </c>
       <c r="I7" t="n">
+        <v>7</v>
+      </c>
+      <c r="J7" t="n">
+        <v>8</v>
+      </c>
+      <c r="K7" t="n">
         <v>5</v>
       </c>
-      <c r="J7" t="n">
+      <c r="L7" t="n">
         <v>0</v>
       </c>
-      <c r="K7" t="n">
+      <c r="M7" t="n">
         <v>21</v>
       </c>
-      <c r="L7" t="n">
+      <c r="N7" t="n">
         <v>12</v>
       </c>
-      <c r="M7" t="n">
+      <c r="O7" t="n">
         <v>11</v>
       </c>
     </row>
@@ -791,9 +837,15 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
         <v>24</v>
       </c>
-      <c r="M8" t="n">
+      <c r="O8" t="n">
         <v>20</v>
       </c>
     </row>
@@ -825,18 +877,24 @@
         <v>11</v>
       </c>
       <c r="I9" t="n">
+        <v>6</v>
+      </c>
+      <c r="J9" t="n">
+        <v>9</v>
+      </c>
+      <c r="K9" t="n">
         <v>5</v>
       </c>
-      <c r="J9" t="n">
-        <v>10</v>
-      </c>
-      <c r="K9" t="n">
-        <v>11</v>
-      </c>
       <c r="L9" t="n">
         <v>10</v>
       </c>
       <c r="M9" t="n">
+        <v>11</v>
+      </c>
+      <c r="N9" t="n">
+        <v>10</v>
+      </c>
+      <c r="O9" t="n">
         <v>10</v>
       </c>
     </row>
@@ -868,18 +926,24 @@
         <v>13</v>
       </c>
       <c r="I10" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="J10" t="n">
         <v>9</v>
       </c>
       <c r="K10" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="L10" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="M10" t="n">
+        <v>11</v>
+      </c>
+      <c r="N10" t="n">
+        <v>11</v>
+      </c>
+      <c r="O10" t="n">
         <v>10</v>
       </c>
     </row>
@@ -911,18 +975,24 @@
         <v>4</v>
       </c>
       <c r="I11" t="n">
+        <v>11</v>
+      </c>
+      <c r="J11" t="n">
+        <v>10</v>
+      </c>
+      <c r="K11" t="n">
         <v>5</v>
       </c>
-      <c r="J11" t="n">
-        <v>11</v>
-      </c>
-      <c r="K11" t="n">
-        <v>11</v>
-      </c>
       <c r="L11" t="n">
         <v>11</v>
       </c>
       <c r="M11" t="n">
+        <v>11</v>
+      </c>
+      <c r="N11" t="n">
+        <v>11</v>
+      </c>
+      <c r="O11" t="n">
         <v>11</v>
       </c>
     </row>
@@ -954,18 +1024,24 @@
         <v>5</v>
       </c>
       <c r="I12" t="n">
+        <v>7</v>
+      </c>
+      <c r="J12" t="n">
+        <v>7</v>
+      </c>
+      <c r="K12" t="n">
         <v>5</v>
       </c>
-      <c r="J12" t="n">
-        <v>11</v>
-      </c>
-      <c r="K12" t="n">
-        <v>11</v>
-      </c>
       <c r="L12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M12" t="n">
+        <v>11</v>
+      </c>
+      <c r="N12" t="n">
+        <v>10</v>
+      </c>
+      <c r="O12" t="n">
         <v>11</v>
       </c>
     </row>
@@ -997,18 +1073,24 @@
         <v>11</v>
       </c>
       <c r="I13" t="n">
+        <v>8</v>
+      </c>
+      <c r="J13" t="n">
+        <v>12</v>
+      </c>
+      <c r="K13" t="n">
         <v>5</v>
       </c>
-      <c r="J13" t="n">
-        <v>11</v>
-      </c>
-      <c r="K13" t="n">
-        <v>11</v>
-      </c>
       <c r="L13" t="n">
         <v>11</v>
       </c>
       <c r="M13" t="n">
+        <v>11</v>
+      </c>
+      <c r="N13" t="n">
+        <v>11</v>
+      </c>
+      <c r="O13" t="n">
         <v>11</v>
       </c>
     </row>
@@ -1040,18 +1122,24 @@
         <v>10</v>
       </c>
       <c r="I14" t="n">
+        <v>9</v>
+      </c>
+      <c r="J14" t="n">
+        <v>9</v>
+      </c>
+      <c r="K14" t="n">
         <v>0</v>
       </c>
-      <c r="J14" t="n">
-        <v>10</v>
-      </c>
-      <c r="K14" t="n">
-        <v>11</v>
-      </c>
       <c r="L14" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="M14" t="n">
+        <v>11</v>
+      </c>
+      <c r="N14" t="n">
+        <v>11</v>
+      </c>
+      <c r="O14" t="n">
         <v>10</v>
       </c>
     </row>
@@ -1083,18 +1171,24 @@
         <v>12</v>
       </c>
       <c r="I15" t="n">
+        <v>11</v>
+      </c>
+      <c r="J15" t="n">
+        <v>9</v>
+      </c>
+      <c r="K15" t="n">
         <v>5</v>
       </c>
-      <c r="J15" t="n">
-        <v>11</v>
-      </c>
-      <c r="K15" t="n">
-        <v>11</v>
-      </c>
       <c r="L15" t="n">
         <v>11</v>
       </c>
       <c r="M15" t="n">
+        <v>11</v>
+      </c>
+      <c r="N15" t="n">
+        <v>11</v>
+      </c>
+      <c r="O15" t="n">
         <v>12</v>
       </c>
     </row>
@@ -1109,7 +1203,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M15"/>
+  <dimension ref="A1:O15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1155,25 +1249,35 @@
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
+          <t>08dec2025</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>09dec2025</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
           <t>26nov2025</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>27nov2025</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>28nov2025</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>29nov2025</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>30nov2025</t>
         </is>
@@ -1218,25 +1322,35 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
       <c r="M2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
         <is>
           <t>11</t>
         </is>
@@ -1285,25 +1399,35 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
       <c r="L3" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
         <is>
           <t>2</t>
         </is>
@@ -1352,25 +1476,35 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
       <c r="L4" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>11</t>
         </is>
@@ -1419,25 +1553,35 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
       <c r="L5" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
         <is>
           <t>10</t>
         </is>
@@ -1486,25 +1630,35 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
         <is>
           <t>12</t>
         </is>
@@ -1549,21 +1703,31 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr">
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>11</t>
         </is>
@@ -1589,12 +1753,14 @@
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr">
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>20</t>
         </is>
@@ -1643,25 +1809,35 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
       <c r="L9" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
         <is>
           <t>10</t>
         </is>
@@ -1710,25 +1886,35 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
       <c r="M10" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
         <is>
           <t>10</t>
         </is>
@@ -1777,25 +1963,35 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
       <c r="L11" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
         <is>
           <t>11</t>
         </is>
@@ -1844,25 +2040,35 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
         <is>
           <t>11</t>
         </is>
@@ -1911,25 +2117,35 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
       <c r="L13" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
         <is>
           <t>11</t>
         </is>
@@ -1976,23 +2192,33 @@
           <t>10</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
         <is>
           <t>10</t>
         </is>
@@ -2041,25 +2267,35 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
       <c r="L15" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
         <is>
           <t>12</t>
         </is>

--- a/data/san_antonio_bajo.xlsx
+++ b/data/san_antonio_bajo.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O15"/>
+  <dimension ref="A1:P15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -482,25 +482,30 @@
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
+          <t>10dec2025</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
           <t>26nov2025</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>27nov2025</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>28nov2025</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>29nov2025</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>30nov2025</t>
         </is>
@@ -540,18 +545,21 @@
         <v>5</v>
       </c>
       <c r="K2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" t="n">
         <v>5</v>
       </c>
-      <c r="L2" t="n">
+      <c r="M2" t="n">
         <v>4</v>
       </c>
-      <c r="M2" t="n">
-        <v>11</v>
-      </c>
       <c r="N2" t="n">
         <v>11</v>
       </c>
       <c r="O2" t="n">
+        <v>11</v>
+      </c>
+      <c r="P2" t="n">
         <v>11</v>
       </c>
     </row>
@@ -589,11 +597,11 @@
         <v>8</v>
       </c>
       <c r="K3" t="n">
+        <v>4</v>
+      </c>
+      <c r="L3" t="n">
         <v>5</v>
       </c>
-      <c r="L3" t="n">
-        <v>10</v>
-      </c>
       <c r="M3" t="n">
         <v>10</v>
       </c>
@@ -601,6 +609,9 @@
         <v>10</v>
       </c>
       <c r="O3" t="n">
+        <v>10</v>
+      </c>
+      <c r="P3" t="n">
         <v>2</v>
       </c>
     </row>
@@ -638,18 +649,21 @@
         <v>9</v>
       </c>
       <c r="K4" t="n">
+        <v>8</v>
+      </c>
+      <c r="L4" t="n">
         <v>5</v>
       </c>
-      <c r="L4" t="n">
-        <v>11</v>
-      </c>
       <c r="M4" t="n">
         <v>11</v>
       </c>
       <c r="N4" t="n">
+        <v>11</v>
+      </c>
+      <c r="O4" t="n">
         <v>2</v>
       </c>
-      <c r="O4" t="n">
+      <c r="P4" t="n">
         <v>11</v>
       </c>
     </row>
@@ -687,11 +701,11 @@
         <v>10</v>
       </c>
       <c r="K5" t="n">
+        <v>9</v>
+      </c>
+      <c r="L5" t="n">
         <v>5</v>
       </c>
-      <c r="L5" t="n">
-        <v>11</v>
-      </c>
       <c r="M5" t="n">
         <v>11</v>
       </c>
@@ -699,6 +713,9 @@
         <v>11</v>
       </c>
       <c r="O5" t="n">
+        <v>11</v>
+      </c>
+      <c r="P5" t="n">
         <v>10</v>
       </c>
     </row>
@@ -736,18 +753,21 @@
         <v>8</v>
       </c>
       <c r="K6" t="n">
+        <v>4</v>
+      </c>
+      <c r="L6" t="n">
         <v>5</v>
       </c>
-      <c r="L6" t="n">
-        <v>11</v>
-      </c>
       <c r="M6" t="n">
         <v>11</v>
       </c>
       <c r="N6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="O6" t="n">
+        <v>10</v>
+      </c>
+      <c r="P6" t="n">
         <v>12</v>
       </c>
     </row>
@@ -785,18 +805,21 @@
         <v>8</v>
       </c>
       <c r="K7" t="n">
+        <v>8</v>
+      </c>
+      <c r="L7" t="n">
         <v>5</v>
       </c>
-      <c r="L7" t="n">
+      <c r="M7" t="n">
         <v>0</v>
       </c>
-      <c r="M7" t="n">
+      <c r="N7" t="n">
         <v>21</v>
       </c>
-      <c r="N7" t="n">
+      <c r="O7" t="n">
         <v>12</v>
       </c>
-      <c r="O7" t="n">
+      <c r="P7" t="n">
         <v>11</v>
       </c>
     </row>
@@ -843,9 +866,12 @@
         <v>0</v>
       </c>
       <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
         <v>24</v>
       </c>
-      <c r="O8" t="n">
+      <c r="P8" t="n">
         <v>20</v>
       </c>
     </row>
@@ -883,18 +909,21 @@
         <v>9</v>
       </c>
       <c r="K9" t="n">
+        <v>9</v>
+      </c>
+      <c r="L9" t="n">
         <v>5</v>
       </c>
-      <c r="L9" t="n">
-        <v>10</v>
-      </c>
       <c r="M9" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N9" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="O9" t="n">
+        <v>10</v>
+      </c>
+      <c r="P9" t="n">
         <v>10</v>
       </c>
     </row>
@@ -932,18 +961,21 @@
         <v>9</v>
       </c>
       <c r="K10" t="n">
+        <v>10</v>
+      </c>
+      <c r="L10" t="n">
         <v>6</v>
       </c>
-      <c r="L10" t="n">
+      <c r="M10" t="n">
         <v>9</v>
       </c>
-      <c r="M10" t="n">
-        <v>11</v>
-      </c>
       <c r="N10" t="n">
         <v>11</v>
       </c>
       <c r="O10" t="n">
+        <v>11</v>
+      </c>
+      <c r="P10" t="n">
         <v>10</v>
       </c>
     </row>
@@ -981,11 +1013,11 @@
         <v>10</v>
       </c>
       <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
         <v>5</v>
       </c>
-      <c r="L11" t="n">
-        <v>11</v>
-      </c>
       <c r="M11" t="n">
         <v>11</v>
       </c>
@@ -993,6 +1025,9 @@
         <v>11</v>
       </c>
       <c r="O11" t="n">
+        <v>11</v>
+      </c>
+      <c r="P11" t="n">
         <v>11</v>
       </c>
     </row>
@@ -1030,18 +1065,21 @@
         <v>7</v>
       </c>
       <c r="K12" t="n">
+        <v>8</v>
+      </c>
+      <c r="L12" t="n">
         <v>5</v>
       </c>
-      <c r="L12" t="n">
-        <v>11</v>
-      </c>
       <c r="M12" t="n">
         <v>11</v>
       </c>
       <c r="N12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="O12" t="n">
+        <v>10</v>
+      </c>
+      <c r="P12" t="n">
         <v>11</v>
       </c>
     </row>
@@ -1079,11 +1117,11 @@
         <v>12</v>
       </c>
       <c r="K13" t="n">
+        <v>6</v>
+      </c>
+      <c r="L13" t="n">
         <v>5</v>
       </c>
-      <c r="L13" t="n">
-        <v>11</v>
-      </c>
       <c r="M13" t="n">
         <v>11</v>
       </c>
@@ -1091,6 +1129,9 @@
         <v>11</v>
       </c>
       <c r="O13" t="n">
+        <v>11</v>
+      </c>
+      <c r="P13" t="n">
         <v>11</v>
       </c>
     </row>
@@ -1128,18 +1169,21 @@
         <v>9</v>
       </c>
       <c r="K14" t="n">
+        <v>9</v>
+      </c>
+      <c r="L14" t="n">
         <v>0</v>
       </c>
-      <c r="L14" t="n">
-        <v>10</v>
-      </c>
       <c r="M14" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N14" t="n">
         <v>11</v>
       </c>
       <c r="O14" t="n">
+        <v>11</v>
+      </c>
+      <c r="P14" t="n">
         <v>10</v>
       </c>
     </row>
@@ -1177,11 +1221,11 @@
         <v>9</v>
       </c>
       <c r="K15" t="n">
+        <v>7</v>
+      </c>
+      <c r="L15" t="n">
         <v>5</v>
       </c>
-      <c r="L15" t="n">
-        <v>11</v>
-      </c>
       <c r="M15" t="n">
         <v>11</v>
       </c>
@@ -1189,6 +1233,9 @@
         <v>11</v>
       </c>
       <c r="O15" t="n">
+        <v>11</v>
+      </c>
+      <c r="P15" t="n">
         <v>12</v>
       </c>
     </row>
@@ -1203,7 +1250,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O15"/>
+  <dimension ref="A1:P15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1259,25 +1306,30 @@
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
+          <t>10dec2025</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
           <t>26nov2025</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>27nov2025</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>28nov2025</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>29nov2025</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>30nov2025</t>
         </is>
@@ -1330,27 +1382,28 @@
           <t>5</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
         <is>
           <t>11</t>
         </is>
@@ -1409,14 +1462,14 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
       <c r="M3" t="inlineStr">
         <is>
           <t>10</t>
@@ -1428,6 +1481,11 @@
         </is>
       </c>
       <c r="O3" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
         <is>
           <t>2</t>
         </is>
@@ -1486,14 +1544,14 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
       <c r="M4" t="inlineStr">
         <is>
           <t>11</t>
@@ -1501,10 +1559,15 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>11</t>
         </is>
@@ -1563,14 +1626,14 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
       <c r="M5" t="inlineStr">
         <is>
           <t>11</t>
@@ -1582,6 +1645,11 @@
         </is>
       </c>
       <c r="O5" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
         <is>
           <t>10</t>
         </is>
@@ -1640,14 +1708,14 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
       <c r="M6" t="inlineStr">
         <is>
           <t>11</t>
@@ -1655,10 +1723,15 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
         <is>
           <t>12</t>
         </is>
@@ -1713,21 +1786,26 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>11</t>
         </is>
@@ -1755,12 +1833,13 @@
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr">
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>20</t>
         </is>
@@ -1819,25 +1898,30 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
         <is>
           <t>10</t>
         </is>
@@ -1896,25 +1980,30 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
         <is>
           <t>10</t>
         </is>
@@ -1971,16 +2060,12 @@
           <t>10</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
       <c r="M11" t="inlineStr">
         <is>
           <t>11</t>
@@ -1992,6 +2077,11 @@
         </is>
       </c>
       <c r="O11" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
         <is>
           <t>11</t>
         </is>
@@ -2050,14 +2140,14 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
       <c r="M12" t="inlineStr">
         <is>
           <t>11</t>
@@ -2065,10 +2155,15 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
         <is>
           <t>11</t>
         </is>
@@ -2127,14 +2222,14 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
       <c r="M13" t="inlineStr">
         <is>
           <t>11</t>
@@ -2146,6 +2241,11 @@
         </is>
       </c>
       <c r="O13" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
         <is>
           <t>11</t>
         </is>
@@ -2202,15 +2302,15 @@
           <t>9</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -2219,6 +2319,11 @@
         </is>
       </c>
       <c r="O14" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
         <is>
           <t>10</t>
         </is>
@@ -2277,14 +2382,14 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
       <c r="M15" t="inlineStr">
         <is>
           <t>11</t>
@@ -2296,6 +2401,11 @@
         </is>
       </c>
       <c r="O15" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
         <is>
           <t>12</t>
         </is>

--- a/data/san_antonio_bajo.xlsx
+++ b/data/san_antonio_bajo.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P15"/>
+  <dimension ref="A1:Q15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -487,25 +487,30 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
+          <t>11dec2025</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
           <t>26nov2025</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>27nov2025</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>28nov2025</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>29nov2025</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>30nov2025</t>
         </is>
@@ -548,18 +553,21 @@
         <v>0</v>
       </c>
       <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
         <v>5</v>
       </c>
-      <c r="M2" t="n">
+      <c r="N2" t="n">
         <v>4</v>
       </c>
-      <c r="N2" t="n">
-        <v>11</v>
-      </c>
       <c r="O2" t="n">
         <v>11</v>
       </c>
       <c r="P2" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q2" t="n">
         <v>11</v>
       </c>
     </row>
@@ -603,7 +611,7 @@
         <v>5</v>
       </c>
       <c r="M3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="N3" t="n">
         <v>10</v>
@@ -612,6 +620,9 @@
         <v>10</v>
       </c>
       <c r="P3" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q3" t="n">
         <v>2</v>
       </c>
     </row>
@@ -652,18 +663,21 @@
         <v>8</v>
       </c>
       <c r="L4" t="n">
+        <v>4</v>
+      </c>
+      <c r="M4" t="n">
         <v>5</v>
       </c>
-      <c r="M4" t="n">
-        <v>11</v>
-      </c>
       <c r="N4" t="n">
         <v>11</v>
       </c>
       <c r="O4" t="n">
+        <v>11</v>
+      </c>
+      <c r="P4" t="n">
         <v>2</v>
       </c>
-      <c r="P4" t="n">
+      <c r="Q4" t="n">
         <v>11</v>
       </c>
     </row>
@@ -707,7 +721,7 @@
         <v>5</v>
       </c>
       <c r="M5" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="N5" t="n">
         <v>11</v>
@@ -716,6 +730,9 @@
         <v>11</v>
       </c>
       <c r="P5" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q5" t="n">
         <v>10</v>
       </c>
     </row>
@@ -756,18 +773,21 @@
         <v>4</v>
       </c>
       <c r="L6" t="n">
+        <v>4</v>
+      </c>
+      <c r="M6" t="n">
         <v>5</v>
       </c>
-      <c r="M6" t="n">
-        <v>11</v>
-      </c>
       <c r="N6" t="n">
         <v>11</v>
       </c>
       <c r="O6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="P6" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q6" t="n">
         <v>12</v>
       </c>
     </row>
@@ -808,18 +828,21 @@
         <v>8</v>
       </c>
       <c r="L7" t="n">
+        <v>3</v>
+      </c>
+      <c r="M7" t="n">
         <v>5</v>
       </c>
-      <c r="M7" t="n">
+      <c r="N7" t="n">
         <v>0</v>
       </c>
-      <c r="N7" t="n">
+      <c r="O7" t="n">
         <v>21</v>
       </c>
-      <c r="O7" t="n">
+      <c r="P7" t="n">
         <v>12</v>
       </c>
-      <c r="P7" t="n">
+      <c r="Q7" t="n">
         <v>11</v>
       </c>
     </row>
@@ -869,9 +892,12 @@
         <v>0</v>
       </c>
       <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
         <v>24</v>
       </c>
-      <c r="P8" t="n">
+      <c r="Q8" t="n">
         <v>20</v>
       </c>
     </row>
@@ -915,15 +941,18 @@
         <v>5</v>
       </c>
       <c r="M9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="N9" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="O9" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="P9" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q9" t="n">
         <v>10</v>
       </c>
     </row>
@@ -964,18 +993,21 @@
         <v>10</v>
       </c>
       <c r="L10" t="n">
+        <v>5</v>
+      </c>
+      <c r="M10" t="n">
         <v>6</v>
       </c>
-      <c r="M10" t="n">
+      <c r="N10" t="n">
         <v>9</v>
       </c>
-      <c r="N10" t="n">
-        <v>11</v>
-      </c>
       <c r="O10" t="n">
         <v>11</v>
       </c>
       <c r="P10" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q10" t="n">
         <v>10</v>
       </c>
     </row>
@@ -1016,11 +1048,11 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
+        <v>4</v>
+      </c>
+      <c r="M11" t="n">
         <v>5</v>
       </c>
-      <c r="M11" t="n">
-        <v>11</v>
-      </c>
       <c r="N11" t="n">
         <v>11</v>
       </c>
@@ -1028,6 +1060,9 @@
         <v>11</v>
       </c>
       <c r="P11" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q11" t="n">
         <v>11</v>
       </c>
     </row>
@@ -1068,18 +1103,21 @@
         <v>8</v>
       </c>
       <c r="L12" t="n">
+        <v>2</v>
+      </c>
+      <c r="M12" t="n">
         <v>5</v>
       </c>
-      <c r="M12" t="n">
-        <v>11</v>
-      </c>
       <c r="N12" t="n">
         <v>11</v>
       </c>
       <c r="O12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="P12" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q12" t="n">
         <v>11</v>
       </c>
     </row>
@@ -1120,11 +1158,11 @@
         <v>6</v>
       </c>
       <c r="L13" t="n">
+        <v>4</v>
+      </c>
+      <c r="M13" t="n">
         <v>5</v>
       </c>
-      <c r="M13" t="n">
-        <v>11</v>
-      </c>
       <c r="N13" t="n">
         <v>11</v>
       </c>
@@ -1132,6 +1170,9 @@
         <v>11</v>
       </c>
       <c r="P13" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q13" t="n">
         <v>11</v>
       </c>
     </row>
@@ -1175,15 +1216,18 @@
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="O14" t="n">
         <v>11</v>
       </c>
       <c r="P14" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q14" t="n">
         <v>10</v>
       </c>
     </row>
@@ -1227,7 +1271,7 @@
         <v>5</v>
       </c>
       <c r="M15" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="N15" t="n">
         <v>11</v>
@@ -1236,6 +1280,9 @@
         <v>11</v>
       </c>
       <c r="P15" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q15" t="n">
         <v>12</v>
       </c>
     </row>
@@ -1250,7 +1297,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P15"/>
+  <dimension ref="A1:Q15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1311,25 +1358,30 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
+          <t>11dec2025</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
           <t>26nov2025</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>27nov2025</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>28nov2025</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>29nov2025</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>30nov2025</t>
         </is>
@@ -1383,27 +1435,28 @@
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr">
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
       <c r="O2" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
         <is>
           <t>11</t>
         </is>
@@ -1472,7 +1525,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -1486,6 +1539,11 @@
         </is>
       </c>
       <c r="P3" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
         <is>
           <t>2</t>
         </is>
@@ -1549,14 +1607,14 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr">
         <is>
           <t>11</t>
@@ -1564,10 +1622,15 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>11</t>
         </is>
@@ -1636,7 +1699,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -1650,6 +1713,11 @@
         </is>
       </c>
       <c r="P5" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
         <is>
           <t>10</t>
         </is>
@@ -1713,14 +1781,14 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr">
         <is>
           <t>11</t>
@@ -1728,10 +1796,15 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
         <is>
           <t>12</t>
         </is>
@@ -1791,21 +1864,26 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr">
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>11</t>
         </is>
@@ -1834,12 +1912,13 @@
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr">
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>20</t>
         </is>
@@ -1908,20 +1987,25 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
         <is>
           <t>10</t>
         </is>
@@ -1985,25 +2069,30 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="N10" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
       <c r="O10" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
         <is>
           <t>10</t>
         </is>
@@ -2063,14 +2152,14 @@
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr">
         <is>
           <t>11</t>
@@ -2082,6 +2171,11 @@
         </is>
       </c>
       <c r="P11" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
         <is>
           <t>11</t>
         </is>
@@ -2145,14 +2239,14 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
       <c r="N12" t="inlineStr">
         <is>
           <t>11</t>
@@ -2160,10 +2254,15 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
         <is>
           <t>11</t>
         </is>
@@ -2227,14 +2326,14 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
       <c r="N13" t="inlineStr">
         <is>
           <t>11</t>
@@ -2246,6 +2345,11 @@
         </is>
       </c>
       <c r="P13" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
         <is>
           <t>11</t>
         </is>
@@ -2308,14 +2412,10 @@
         </is>
       </c>
       <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+      <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
@@ -2324,6 +2424,11 @@
         </is>
       </c>
       <c r="P14" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
         <is>
           <t>10</t>
         </is>
@@ -2392,7 +2497,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -2406,6 +2511,11 @@
         </is>
       </c>
       <c r="P15" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
         <is>
           <t>12</t>
         </is>

--- a/data/san_antonio_bajo.xlsx
+++ b/data/san_antonio_bajo.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q15"/>
+  <dimension ref="A1:T16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -492,25 +492,40 @@
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
+          <t>12dec2025</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>13dec2025</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>14dec2025</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
           <t>26nov2025</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>27nov2025</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>28nov2025</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>29nov2025</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>30nov2025</t>
         </is>
@@ -556,18 +571,27 @@
         <v>0</v>
       </c>
       <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="n">
+        <v>3</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2" t="n">
         <v>5</v>
       </c>
-      <c r="N2" t="n">
+      <c r="Q2" t="n">
         <v>4</v>
       </c>
-      <c r="O2" t="n">
-        <v>11</v>
-      </c>
-      <c r="P2" t="n">
-        <v>11</v>
-      </c>
-      <c r="Q2" t="n">
+      <c r="R2" t="n">
+        <v>11</v>
+      </c>
+      <c r="S2" t="n">
+        <v>11</v>
+      </c>
+      <c r="T2" t="n">
         <v>11</v>
       </c>
     </row>
@@ -611,18 +635,27 @@
         <v>5</v>
       </c>
       <c r="M3" t="n">
+        <v>4</v>
+      </c>
+      <c r="N3" t="n">
+        <v>4</v>
+      </c>
+      <c r="O3" t="n">
+        <v>4</v>
+      </c>
+      <c r="P3" t="n">
         <v>5</v>
       </c>
-      <c r="N3" t="n">
-        <v>10</v>
-      </c>
-      <c r="O3" t="n">
-        <v>10</v>
-      </c>
-      <c r="P3" t="n">
-        <v>10</v>
-      </c>
       <c r="Q3" t="n">
+        <v>10</v>
+      </c>
+      <c r="R3" t="n">
+        <v>10</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="n">
         <v>2</v>
       </c>
     </row>
@@ -666,623 +699,795 @@
         <v>4</v>
       </c>
       <c r="M4" t="n">
+        <v>4</v>
+      </c>
+      <c r="N4" t="n">
+        <v>4</v>
+      </c>
+      <c r="O4" t="n">
         <v>5</v>
       </c>
-      <c r="N4" t="n">
-        <v>11</v>
-      </c>
-      <c r="O4" t="n">
-        <v>11</v>
-      </c>
       <c r="P4" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>11</v>
+      </c>
+      <c r="R4" t="n">
+        <v>11</v>
+      </c>
+      <c r="S4" t="n">
         <v>2</v>
       </c>
-      <c r="Q4" t="n">
+      <c r="T4" t="n">
         <v>11</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>MEDINA VALLEJOS ERICK LEONARDO</t>
+          <t>GALLARDO SAUCEDO CÉSAR MELANIO</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="N5" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>10</v>
+        <v>0</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>PÓSITO CHUGDEN NANIX</t>
+          <t>MEDINA VALLEJOS ERICK LEONARDO</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C6" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D6" t="n">
+        <v>14</v>
+      </c>
+      <c r="E6" t="n">
+        <v>11</v>
+      </c>
+      <c r="F6" t="n">
+        <v>10</v>
+      </c>
+      <c r="G6" t="n">
+        <v>10</v>
+      </c>
+      <c r="H6" t="n">
         <v>13</v>
       </c>
-      <c r="E6" t="n">
-        <v>11</v>
-      </c>
-      <c r="F6" t="n">
-        <v>12</v>
-      </c>
-      <c r="G6" t="n">
-        <v>13</v>
-      </c>
-      <c r="H6" t="n">
-        <v>10</v>
-      </c>
       <c r="I6" t="n">
+        <v>10</v>
+      </c>
+      <c r="J6" t="n">
+        <v>10</v>
+      </c>
+      <c r="K6" t="n">
         <v>9</v>
       </c>
-      <c r="J6" t="n">
-        <v>8</v>
-      </c>
-      <c r="K6" t="n">
-        <v>4</v>
-      </c>
       <c r="L6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M6" t="n">
         <v>5</v>
       </c>
       <c r="N6" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="O6" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="P6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="Q6" t="n">
-        <v>12</v>
+        <v>11</v>
+      </c>
+      <c r="R6" t="n">
+        <v>11</v>
+      </c>
+      <c r="S6" t="n">
+        <v>11</v>
+      </c>
+      <c r="T6" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>ROJAS VASQUEZ FLOR NOELITA</t>
+          <t>PÓSITO CHUGDEN NANIX</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C7" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="D7" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E7" t="n">
+        <v>11</v>
+      </c>
+      <c r="F7" t="n">
+        <v>12</v>
+      </c>
+      <c r="G7" t="n">
         <v>13</v>
       </c>
-      <c r="F7" t="n">
-        <v>7</v>
-      </c>
-      <c r="G7" t="n">
-        <v>0</v>
-      </c>
       <c r="H7" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="I7" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="J7" t="n">
         <v>8</v>
       </c>
       <c r="K7" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="L7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M7" t="n">
+        <v>4</v>
+      </c>
+      <c r="N7" t="n">
+        <v>4</v>
+      </c>
+      <c r="O7" t="n">
         <v>5</v>
       </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>21</v>
-      </c>
       <c r="P7" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>11</v>
+      </c>
+      <c r="R7" t="n">
+        <v>11</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="n">
         <v>12</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>11</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>RUIZ RUIZ LUZ MERI</t>
+          <t>ROJAS VASQUEZ FLOR NOELITA</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="C8" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P8" t="n">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="Q8" t="n">
-        <v>20</v>
+        <v>0</v>
+      </c>
+      <c r="R8" t="n">
+        <v>21</v>
+      </c>
+      <c r="S8" t="n">
+        <v>12</v>
+      </c>
+      <c r="T8" t="n">
+        <v>11</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>SOTO VALLEJOS ELSITA</t>
+          <t>RUIZ RUIZ LUZ MERI</t>
         </is>
       </c>
       <c r="B9" t="n">
+        <v>25</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
+        <v>24</v>
+      </c>
+      <c r="T9" t="n">
         <v>20</v>
-      </c>
-      <c r="C9" t="n">
-        <v>12</v>
-      </c>
-      <c r="D9" t="n">
-        <v>18</v>
-      </c>
-      <c r="E9" t="n">
-        <v>10</v>
-      </c>
-      <c r="F9" t="n">
-        <v>9</v>
-      </c>
-      <c r="G9" t="n">
-        <v>11</v>
-      </c>
-      <c r="H9" t="n">
-        <v>11</v>
-      </c>
-      <c r="I9" t="n">
-        <v>6</v>
-      </c>
-      <c r="J9" t="n">
-        <v>9</v>
-      </c>
-      <c r="K9" t="n">
-        <v>9</v>
-      </c>
-      <c r="L9" t="n">
-        <v>5</v>
-      </c>
-      <c r="M9" t="n">
-        <v>5</v>
-      </c>
-      <c r="N9" t="n">
-        <v>10</v>
-      </c>
-      <c r="O9" t="n">
-        <v>11</v>
-      </c>
-      <c r="P9" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>10</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>SOTO VILLENA NILSON</t>
+          <t>SOTO VALLEJOS ELSITA</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="C10" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="D10" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E10" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F10" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G10" t="n">
         <v>10</v>
       </c>
       <c r="H10" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="I10" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="J10" t="n">
         <v>9</v>
       </c>
       <c r="K10" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="L10" t="n">
         <v>5</v>
       </c>
       <c r="M10" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="N10" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="O10" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="P10" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="Q10" t="n">
+        <v>10</v>
+      </c>
+      <c r="R10" t="n">
+        <v>11</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="n">
         <v>10</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>TELLO FERNANDEZ MILENY</t>
+          <t>SOTO VILLENA NILSON</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C11" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D11" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E11" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F11" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="G11" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="H11" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="I11" t="n">
         <v>11</v>
       </c>
       <c r="J11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M11" t="n">
         <v>5</v>
       </c>
       <c r="N11" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="O11" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="P11" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="Q11" t="n">
-        <v>11</v>
+        <v>9</v>
+      </c>
+      <c r="R11" t="n">
+        <v>11</v>
+      </c>
+      <c r="S11" t="n">
+        <v>11</v>
+      </c>
+      <c r="T11" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>TIRADO PEREZ JEINER</t>
+          <t>TELLO FERNANDEZ MILENY</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>14</v>
       </c>
       <c r="C12" t="n">
+        <v>12</v>
+      </c>
+      <c r="D12" t="n">
+        <v>16</v>
+      </c>
+      <c r="E12" t="n">
+        <v>10</v>
+      </c>
+      <c r="F12" t="n">
         <v>15</v>
-      </c>
-      <c r="D12" t="n">
-        <v>18</v>
-      </c>
-      <c r="E12" t="n">
-        <v>15</v>
-      </c>
-      <c r="F12" t="n">
-        <v>7</v>
       </c>
       <c r="G12" t="n">
         <v>3</v>
       </c>
       <c r="H12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I12" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="J12" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="K12" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M12" t="n">
         <v>5</v>
       </c>
       <c r="N12" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="P12" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="Q12" t="n">
+        <v>11</v>
+      </c>
+      <c r="R12" t="n">
+        <v>11</v>
+      </c>
+      <c r="S12" t="n">
+        <v>11</v>
+      </c>
+      <c r="T12" t="n">
         <v>11</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>VASQUEZ DIAZ LUZ ANGELICA</t>
+          <t>TIRADO PEREZ JEINER</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="C13" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D13" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E13" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F13" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="G13" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="H13" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="I13" t="n">
+        <v>7</v>
+      </c>
+      <c r="J13" t="n">
+        <v>7</v>
+      </c>
+      <c r="K13" t="n">
         <v>8</v>
       </c>
-      <c r="J13" t="n">
-        <v>12</v>
-      </c>
-      <c r="K13" t="n">
-        <v>6</v>
-      </c>
       <c r="L13" t="n">
+        <v>2</v>
+      </c>
+      <c r="M13" t="n">
         <v>4</v>
       </c>
-      <c r="M13" t="n">
+      <c r="N13" t="n">
+        <v>3</v>
+      </c>
+      <c r="O13" t="n">
         <v>5</v>
       </c>
-      <c r="N13" t="n">
-        <v>11</v>
-      </c>
-      <c r="O13" t="n">
-        <v>11</v>
-      </c>
       <c r="P13" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="Q13" t="n">
+        <v>11</v>
+      </c>
+      <c r="R13" t="n">
+        <v>11</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="n">
         <v>11</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>VASQUEZ LUNA YUDITH</t>
+          <t>VASQUEZ DIAZ LUZ ANGELICA</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="C14" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="D14" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E14" t="n">
         <v>10</v>
       </c>
       <c r="F14" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G14" t="n">
         <v>10</v>
       </c>
       <c r="H14" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I14" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J14" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="K14" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N14" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="O14" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="P14" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="Q14" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R14" t="n">
+        <v>11</v>
+      </c>
+      <c r="S14" t="n">
+        <v>11</v>
+      </c>
+      <c r="T14" t="n">
+        <v>11</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>ZAMORA TAMAY NEYSER IVAN</t>
+          <t>VASQUEZ LUNA YUDITH</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="D15" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E15" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F15" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="G15" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="H15" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="I15" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="J15" t="n">
         <v>9</v>
       </c>
       <c r="K15" t="n">
+        <v>8</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>4</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>10</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>10</v>
+      </c>
+      <c r="R15" t="n">
+        <v>11</v>
+      </c>
+      <c r="S15" t="n">
+        <v>11</v>
+      </c>
+      <c r="T15" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>ZAMORA TAMAY NEYSER IVAN</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>13</v>
+      </c>
+      <c r="C16" t="n">
+        <v>20</v>
+      </c>
+      <c r="D16" t="n">
+        <v>18</v>
+      </c>
+      <c r="E16" t="n">
+        <v>14</v>
+      </c>
+      <c r="F16" t="n">
+        <v>15</v>
+      </c>
+      <c r="G16" t="n">
+        <v>15</v>
+      </c>
+      <c r="H16" t="n">
+        <v>12</v>
+      </c>
+      <c r="I16" t="n">
+        <v>11</v>
+      </c>
+      <c r="J16" t="n">
+        <v>9</v>
+      </c>
+      <c r="K16" t="n">
         <v>7</v>
       </c>
-      <c r="L15" t="n">
+      <c r="L16" t="n">
         <v>5</v>
       </c>
-      <c r="M15" t="n">
+      <c r="M16" t="n">
+        <v>6</v>
+      </c>
+      <c r="N16" t="n">
+        <v>7</v>
+      </c>
+      <c r="O16" t="n">
+        <v>7</v>
+      </c>
+      <c r="P16" t="n">
         <v>5</v>
       </c>
-      <c r="N15" t="n">
-        <v>11</v>
-      </c>
-      <c r="O15" t="n">
-        <v>11</v>
-      </c>
-      <c r="P15" t="n">
-        <v>11</v>
-      </c>
-      <c r="Q15" t="n">
+      <c r="Q16" t="n">
+        <v>11</v>
+      </c>
+      <c r="R16" t="n">
+        <v>11</v>
+      </c>
+      <c r="S16" t="n">
+        <v>11</v>
+      </c>
+      <c r="T16" t="n">
         <v>12</v>
       </c>
     </row>
@@ -1297,7 +1502,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q15"/>
+  <dimension ref="A1:T16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1363,25 +1568,40 @@
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
+          <t>12dec2025</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>13dec2025</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>14dec2025</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
           <t>26nov2025</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>27nov2025</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>28nov2025</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>29nov2025</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>30nov2025</t>
         </is>
@@ -1436,27 +1656,34 @@
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
         <is>
           <t>11</t>
         </is>
@@ -1525,25 +1752,40 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
       <c r="Q3" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
         <is>
           <t>2</t>
         </is>
@@ -1612,25 +1854,40 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>11</t>
         </is>
@@ -1639,407 +1896,398 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>MEDINA VALLEJOS ERICK LEONARDO</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>GALLARDO SAUCEDO CÉSAR MELANIO</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>PÓSITO CHUGDEN NANIX</t>
+          <t>MEDINA VALLEJOS ERICK LEONARDO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
       <c r="I6" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>10</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>ROJAS VASQUEZ FLOR NOELITA</t>
+          <t>PÓSITO CHUGDEN NANIX</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>18</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
           <t>12</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>11</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>RUIZ RUIZ LUZ MERI</t>
+          <t>ROJAS VASQUEZ FLOR NOELITA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr"/>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>20</t>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>11</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>SOTO VALLEJOS ELSITA</t>
+          <t>RUIZ RUIZ LUZ MERI</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
           <t>20</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>10</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>SOTO VILLENA NILSON</t>
+          <t>SOTO VALLEJOS ELSITA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>12</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>18</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -2049,12 +2297,12 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -2064,7 +2312,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -2074,25 +2322,40 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
         <is>
           <t>10</t>
         </is>
@@ -2101,90 +2364,109 @@
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>TELLO FERNANDEZ MILENY</t>
+          <t>SOTO VILLENA NILSON</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>19</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>10</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>10</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>TIRADO PEREZ JEINER</t>
+          <t>TELLO FERNANDEZ MILENY</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -2194,24 +2476,24 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
       <c r="G12" t="inlineStr">
         <is>
           <t>3</t>
@@ -2219,50 +2501,57 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
+      <c r="P12" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
       <c r="Q12" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
         <is>
           <t>11</t>
         </is>
@@ -2271,85 +2560,100 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>VASQUEZ DIAZ LUZ ANGELICA</t>
+          <t>TIRADO PEREZ JEINER</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>14</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>15</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>18</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>15</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>7</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="L13" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr">
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
         <is>
           <t>11</t>
         </is>
@@ -2358,22 +2662,22 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>VASQUEZ LUNA YUDITH</t>
+          <t>VASQUEZ DIAZ LUZ ANGELICA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>12</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>16</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -2383,7 +2687,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>12</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -2393,129 +2697,257 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>11</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>6</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>11</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
+          <t>VASQUEZ LUNA YUDITH</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
           <t>ZAMORA TAMAY NEYSER IVAN</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
+      <c r="H16" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr">
+      <c r="K16" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr">
+      <c r="L16" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="M15" t="inlineStr">
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="Q15" t="inlineStr">
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
         <is>
           <t>12</t>
         </is>

--- a/data/san_antonio_bajo.xlsx
+++ b/data/san_antonio_bajo.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T16"/>
+  <dimension ref="A1:U16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -507,25 +507,30 @@
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
+          <t>15dec2025</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
           <t>26nov2025</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>27nov2025</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>28nov2025</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>29nov2025</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>30nov2025</t>
         </is>
@@ -580,18 +585,21 @@
         <v>0</v>
       </c>
       <c r="P2" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q2" t="n">
         <v>5</v>
       </c>
-      <c r="Q2" t="n">
+      <c r="R2" t="n">
         <v>4</v>
       </c>
-      <c r="R2" t="n">
-        <v>11</v>
-      </c>
       <c r="S2" t="n">
         <v>11</v>
       </c>
       <c r="T2" t="n">
+        <v>11</v>
+      </c>
+      <c r="U2" t="n">
         <v>11</v>
       </c>
     </row>
@@ -644,11 +652,11 @@
         <v>4</v>
       </c>
       <c r="P3" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q3" t="n">
         <v>5</v>
       </c>
-      <c r="Q3" t="n">
-        <v>10</v>
-      </c>
       <c r="R3" t="n">
         <v>10</v>
       </c>
@@ -656,6 +664,9 @@
         <v>10</v>
       </c>
       <c r="T3" t="n">
+        <v>10</v>
+      </c>
+      <c r="U3" t="n">
         <v>2</v>
       </c>
     </row>
@@ -708,18 +719,21 @@
         <v>5</v>
       </c>
       <c r="P4" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q4" t="n">
         <v>5</v>
       </c>
-      <c r="Q4" t="n">
-        <v>11</v>
-      </c>
       <c r="R4" t="n">
         <v>11</v>
       </c>
       <c r="S4" t="n">
+        <v>11</v>
+      </c>
+      <c r="T4" t="n">
         <v>2</v>
       </c>
-      <c r="T4" t="n">
+      <c r="U4" t="n">
         <v>11</v>
       </c>
     </row>
@@ -786,6 +800,9 @@
       <c r="T5" t="n">
         <v>0</v>
       </c>
+      <c r="U5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
@@ -836,11 +853,11 @@
         <v>5</v>
       </c>
       <c r="P6" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q6" t="n">
         <v>5</v>
       </c>
-      <c r="Q6" t="n">
-        <v>11</v>
-      </c>
       <c r="R6" t="n">
         <v>11</v>
       </c>
@@ -848,6 +865,9 @@
         <v>11</v>
       </c>
       <c r="T6" t="n">
+        <v>11</v>
+      </c>
+      <c r="U6" t="n">
         <v>10</v>
       </c>
     </row>
@@ -897,21 +917,24 @@
         <v>4</v>
       </c>
       <c r="O7" t="n">
+        <v>4</v>
+      </c>
+      <c r="P7" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q7" t="n">
         <v>5</v>
       </c>
-      <c r="P7" t="n">
-        <v>5</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>11</v>
-      </c>
       <c r="R7" t="n">
         <v>11</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T7" t="n">
+        <v>10</v>
+      </c>
+      <c r="U7" t="n">
         <v>12</v>
       </c>
     </row>
@@ -964,18 +987,21 @@
         <v>3</v>
       </c>
       <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
         <v>5</v>
       </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
       <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
         <v>21</v>
       </c>
-      <c r="S8" t="n">
+      <c r="T8" t="n">
         <v>12</v>
       </c>
-      <c r="T8" t="n">
+      <c r="U8" t="n">
         <v>11</v>
       </c>
     </row>
@@ -1037,9 +1063,12 @@
         <v>0</v>
       </c>
       <c r="S9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" t="n">
         <v>24</v>
       </c>
-      <c r="T9" t="n">
+      <c r="U9" t="n">
         <v>20</v>
       </c>
     </row>
@@ -1092,18 +1121,21 @@
         <v>5</v>
       </c>
       <c r="P10" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q10" t="n">
         <v>5</v>
       </c>
-      <c r="Q10" t="n">
-        <v>10</v>
-      </c>
       <c r="R10" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T10" t="n">
+        <v>10</v>
+      </c>
+      <c r="U10" t="n">
         <v>10</v>
       </c>
     </row>
@@ -1156,18 +1188,21 @@
         <v>4</v>
       </c>
       <c r="P11" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q11" t="n">
         <v>6</v>
       </c>
-      <c r="Q11" t="n">
+      <c r="R11" t="n">
         <v>9</v>
       </c>
-      <c r="R11" t="n">
-        <v>11</v>
-      </c>
       <c r="S11" t="n">
         <v>11</v>
       </c>
       <c r="T11" t="n">
+        <v>11</v>
+      </c>
+      <c r="U11" t="n">
         <v>10</v>
       </c>
     </row>
@@ -1220,11 +1255,11 @@
         <v>2</v>
       </c>
       <c r="P12" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q12" t="n">
         <v>5</v>
       </c>
-      <c r="Q12" t="n">
-        <v>11</v>
-      </c>
       <c r="R12" t="n">
         <v>11</v>
       </c>
@@ -1232,6 +1267,9 @@
         <v>11</v>
       </c>
       <c r="T12" t="n">
+        <v>11</v>
+      </c>
+      <c r="U12" t="n">
         <v>11</v>
       </c>
     </row>
@@ -1284,18 +1322,21 @@
         <v>5</v>
       </c>
       <c r="P13" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q13" t="n">
         <v>5</v>
       </c>
-      <c r="Q13" t="n">
-        <v>11</v>
-      </c>
       <c r="R13" t="n">
         <v>11</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T13" t="n">
+        <v>10</v>
+      </c>
+      <c r="U13" t="n">
         <v>11</v>
       </c>
     </row>
@@ -1348,11 +1389,11 @@
         <v>6</v>
       </c>
       <c r="P14" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q14" t="n">
         <v>5</v>
       </c>
-      <c r="Q14" t="n">
-        <v>11</v>
-      </c>
       <c r="R14" t="n">
         <v>11</v>
       </c>
@@ -1360,6 +1401,9 @@
         <v>11</v>
       </c>
       <c r="T14" t="n">
+        <v>11</v>
+      </c>
+      <c r="U14" t="n">
         <v>11</v>
       </c>
     </row>
@@ -1391,7 +1435,7 @@
         <v>10</v>
       </c>
       <c r="I15" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J15" t="n">
         <v>9</v>
@@ -1412,18 +1456,21 @@
         <v>10</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q15" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="S15" t="n">
         <v>11</v>
       </c>
       <c r="T15" t="n">
+        <v>11</v>
+      </c>
+      <c r="U15" t="n">
         <v>10</v>
       </c>
     </row>
@@ -1479,7 +1526,7 @@
         <v>5</v>
       </c>
       <c r="Q16" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="R16" t="n">
         <v>11</v>
@@ -1488,6 +1535,9 @@
         <v>11</v>
       </c>
       <c r="T16" t="n">
+        <v>11</v>
+      </c>
+      <c r="U16" t="n">
         <v>12</v>
       </c>
     </row>
@@ -1502,7 +1552,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T16"/>
+  <dimension ref="A1:U16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1583,25 +1633,30 @@
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
+          <t>15dec2025</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
           <t>26nov2025</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>27nov2025</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>28nov2025</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>29nov2025</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>30nov2025</t>
         </is>
@@ -1665,25 +1720,30 @@
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="R2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
       <c r="S2" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
         <is>
           <t>11</t>
         </is>
@@ -1767,14 +1827,14 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
       <c r="R3" t="inlineStr">
         <is>
           <t>10</t>
@@ -1786,6 +1846,11 @@
         </is>
       </c>
       <c r="T3" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
         <is>
           <t>2</t>
         </is>
@@ -1869,14 +1934,14 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
       <c r="R4" t="inlineStr">
         <is>
           <t>11</t>
@@ -1884,10 +1949,15 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>11</t>
         </is>
@@ -1922,6 +1992,7 @@
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="inlineStr"/>
       <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
@@ -2001,14 +2072,14 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
       <c r="R6" t="inlineStr">
         <is>
           <t>11</t>
@@ -2020,6 +2091,11 @@
         </is>
       </c>
       <c r="T6" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
         <is>
           <t>10</t>
         </is>
@@ -2098,19 +2174,19 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
       <c r="R7" t="inlineStr">
         <is>
           <t>11</t>
@@ -2118,10 +2194,15 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
         <is>
           <t>12</t>
         </is>
@@ -2199,23 +2280,24 @@
           <t>3</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr"/>
-      <c r="R8" t="inlineStr">
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>11</t>
         </is>
@@ -2248,12 +2330,13 @@
       <c r="P9" t="inlineStr"/>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr"/>
-      <c r="S9" t="inlineStr">
+      <c r="S9" t="inlineStr"/>
+      <c r="T9" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>20</t>
         </is>
@@ -2337,25 +2420,30 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
         <is>
           <t>10</t>
         </is>
@@ -2439,25 +2527,30 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr">
+      <c r="R11" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
       <c r="S11" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
         <is>
           <t>10</t>
         </is>
@@ -2533,14 +2626,14 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
       <c r="R12" t="inlineStr">
         <is>
           <t>11</t>
@@ -2552,6 +2645,11 @@
         </is>
       </c>
       <c r="T12" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
         <is>
           <t>11</t>
         </is>
@@ -2635,14 +2733,14 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="Q13" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
       <c r="R13" t="inlineStr">
         <is>
           <t>11</t>
@@ -2650,10 +2748,15 @@
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
         <is>
           <t>11</t>
         </is>
@@ -2737,14 +2840,14 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="Q14" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
       <c r="R14" t="inlineStr">
         <is>
           <t>11</t>
@@ -2756,6 +2859,11 @@
         </is>
       </c>
       <c r="T14" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
         <is>
           <t>11</t>
         </is>
@@ -2804,7 +2912,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2829,15 +2937,15 @@
           <t>10</t>
         </is>
       </c>
-      <c r="P15" t="inlineStr"/>
-      <c r="Q15" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
@@ -2846,6 +2954,11 @@
         </is>
       </c>
       <c r="T15" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
         <is>
           <t>10</t>
         </is>
@@ -2934,7 +3047,7 @@
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>5</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
@@ -2948,6 +3061,11 @@
         </is>
       </c>
       <c r="T16" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
         <is>
           <t>12</t>
         </is>
